--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3897"/>
+  <dimension ref="A1:E3898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105635,6 +105635,33 @@
         </is>
       </c>
     </row>
+    <row r="3898">
+      <c r="A3898" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3898" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3898" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3898" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3898" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3900"/>
+  <dimension ref="A1:E3902"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105716,6 +105716,60 @@
         </is>
       </c>
     </row>
+    <row r="3901">
+      <c r="A3901" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B3901" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3901" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3901" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3901" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="3902">
+      <c r="A3902" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3902" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3902" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D3902" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E3902" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3904"/>
+  <dimension ref="A1:E3906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -105821,6 +105833,60 @@
       <c r="E3904" t="inlineStr">
         <is>
           <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="3905">
+      <c r="A3905" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B3905" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3905" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3905" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3905" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="3906">
+      <c r="A3906" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3906" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3906" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D3906" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3906" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
